--- a/xls/square_12_tri3_20.xlsx
+++ b/xls/square_12_tri3_20.xlsx
@@ -482,13 +482,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.599879181227858</v>
+        <v>-0.5998791577368077</v>
       </c>
       <c r="J20">
-        <v>-0.5638882938932318</v>
+        <v>-0.5638882766342066</v>
       </c>
       <c r="K20">
-        <v>3.858500851094436</v>
+        <v>3.8585008447941003</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.2931773964001614</v>
+        <v>-0.29317739755904665</v>
       </c>
       <c r="J21">
-        <v>-0.30497766887488964</v>
+        <v>-0.30497767000464027</v>
       </c>
       <c r="K21">
-        <v>3.9508775676990147</v>
+        <v>3.9508775687741577</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.0004515042461800328</v>
+        <v>-0.0004515042482684289</v>
       </c>
       <c r="J22">
-        <v>-0.00028955146980254087</v>
+        <v>-0.00028955147094482484</v>
       </c>
       <c r="K22">
-        <v>2.464331480496391</v>
+        <v>2.4643314811131054</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.0017281295026395928</v>
+        <v>-0.0017281295017064684</v>
       </c>
       <c r="J23">
-        <v>-0.0011989781141839542</v>
+        <v>-0.0011989781135314272</v>
       </c>
       <c r="K23">
-        <v>2.8154641672858607</v>
+        <v>2.8154641673247105</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-9.028126618992297e-5</v>
+        <v>-9.02812661943598e-5</v>
       </c>
       <c r="J24">
-        <v>-6.992104416575932e-5</v>
+        <v>-6.992104416879744e-5</v>
       </c>
       <c r="K24">
-        <v>2.2782830269318013</v>
+        <v>2.278283026727075</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.00024814114560645903</v>
+        <v>-0.00024814114569083766</v>
       </c>
       <c r="J25">
-        <v>-0.00018033019642101626</v>
+        <v>-0.00018033019647547516</v>
       </c>
       <c r="K25">
-        <v>2.4450416027052553</v>
+        <v>2.445041602641779</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.00011439012896796748</v>
+        <v>-0.00011439012897375498</v>
       </c>
       <c r="J26">
-        <v>-8.60997559819898e-5</v>
+        <v>-8.6099755986089e-5</v>
       </c>
       <c r="K26">
-        <v>2.308525078198083</v>
+        <v>2.3085250782316296</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-9.545038757466982e-5</v>
+        <v>-9.54503875642528e-5</v>
       </c>
       <c r="J27">
-        <v>-7.360424159877302e-5</v>
+        <v>-7.360424159327541e-5</v>
       </c>
       <c r="K27">
-        <v>2.2870573563365717</v>
+        <v>2.28705735650612</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.0001249598428931166</v>
+        <v>-0.00012495984288679845</v>
       </c>
       <c r="J28">
-        <v>-9.438021206808568e-5</v>
+        <v>-9.438021206442044e-5</v>
       </c>
       <c r="K28">
-        <v>2.3279885507059483</v>
+        <v>2.327988550756738</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-8.400690753017389e-5</v>
+        <v>-8.400690753634678e-5</v>
       </c>
       <c r="J29">
-        <v>-6.23016960057128e-5</v>
+        <v>-6.230169600995647e-5</v>
       </c>
       <c r="K29">
-        <v>2.239984080600498</v>
+        <v>2.239984080650676</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.00014443606976727644</v>
+        <v>-0.0001444360697303304</v>
       </c>
       <c r="J30">
-        <v>-0.00011262976012353944</v>
+        <v>-0.00011262976009783344</v>
       </c>
       <c r="K30">
-        <v>2.3884436321441918</v>
+        <v>2.388443632140294</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-4.55064128718356e-6</v>
+        <v>-4.550641288051464e-6</v>
       </c>
       <c r="J31">
-        <v>-8.402548021661215e-6</v>
+        <v>-8.402548021902301e-6</v>
       </c>
       <c r="K31">
-        <v>2.0117952242757533</v>
+        <v>2.0117952244302324</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -902,13 +902,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-2.0361027903198897e-5</v>
+        <v>-2.0361027903873958e-5</v>
       </c>
       <c r="J32">
-        <v>-1.557027605306769e-5</v>
+        <v>-1.5570276053549874e-5</v>
       </c>
       <c r="K32">
-        <v>1.952703109706245</v>
+        <v>1.9527031095003395</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_20.xlsx
+++ b/xls/square_12_tri3_20.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>441</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>1.654113680970334</v>
+      </c>
+      <c r="J18">
+        <v>-1.243702165202109</v>
+      </c>
+      <c r="K18">
+        <v>3.235447156390964</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>441</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>-0.6007444861361115</v>
+      </c>
+      <c r="J19">
+        <v>-0.8646957741881955</v>
+      </c>
+      <c r="K19">
+        <v>3.5048849099502455</v>
+      </c>
+    </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>11</v>
